--- a/crib/data_excel.xlsx
+++ b/crib/data_excel.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC880EDF-441E-43FD-8AB5-41E58DE68611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{4580139E-8B0A-4BF3-A599-CCC1FCBD3D07}"/>
+    <workbookView xWindow="3250" yWindow="1610" windowWidth="8670" windowHeight="7100" activeTab="1" xr2:uid="{4580139E-8B0A-4BF3-A599-CCC1FCBD3D07}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -21,6 +21,7 @@
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -13660,7 +13661,7 @@
         <v>2</v>
       </c>
       <c r="AD66">
-        <f t="shared" ref="AD66:AD97" si="4">AA66+AB66+AC66</f>
+        <f t="shared" ref="AD66:AD85" si="4">AA66+AB66+AC66</f>
         <v>11</v>
       </c>
       <c r="AE66">
